--- a/out/LSTM-mamba2_repeat_5_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7867500136927612</v>
+        <v>5.448042895279977</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7867500136927612</v>
+        <v>5.448042895279977</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386750013692761</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.503542575915646</v>
+        <v>-0.04098559548271052</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.04098559548271052</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915646</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915646</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915646</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915646</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.04098559548271052</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002591839305629255</v>
+        <v>-2.642178744846023e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3335896976288547</v>
+        <v>0.03400689860423536</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.503542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6678111293160394</v>
+        <v>0.06807815461889793</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07703967000539425</v>
+        <v>-0.007853590681102267</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.503542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2562908436928973</v>
+        <v>0.02612688613568468</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2562908436928973</v>
+        <v>0.02612688613568468</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2560183975694678</v>
+        <v>0.02607970246946358</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8370134129136547</v>
+        <v>0.1449582647414449</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.931711912735299</v>
+        <v>0.3162852029227524</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1601530853837934</v>
+        <v>0.02773613061875513</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.41378321331946</v>
+        <v>0.2265874605544962</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2805231001256899</v>
+        <v>0.04858246322038667</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.814755269477365</v>
+        <v>0.2960301637613131</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1536246580315473</v>
+        <v>0.02660576306624786</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.84123973296507</v>
+        <v>0.3006169160772276</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06344922104707135</v>
+        <v>0.01098755827967764</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.814352387472299</v>
+        <v>0.2959595849574902</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07905277499944022</v>
+        <v>0.0136901234083854</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.909018972535161</v>
+        <v>0.3123543370732905</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04759939139119661</v>
+        <v>0.008241188079415353</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.925112517321712</v>
+        <v>0.3151393581434789</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0361883335185099</v>
+        <v>0.006265160402021513</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.949870068940208</v>
+        <v>0.3194244908575015</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01600698848396014</v>
+        <v>0.002768314654405888</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.945661997331182</v>
+        <v>0.3186915370392266</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01269938090335914</v>
+        <v>0.002194368701157271</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.955051553490028</v>
+        <v>0.3203136847957477</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006296228783265414</v>
+        <v>0.001085645394801</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.954934092195183</v>
+        <v>0.3202891987258513</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003657683738747592</v>
+        <v>0.00062920576254724</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.955952813739853</v>
+        <v>0.32046179701314</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001827796469746611</v>
+        <v>0.00031210288127362</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.955945531784525</v>
+        <v>0.3204564021986467</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009005141711502362</v>
+        <v>0.0001531056489309936</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.955917609602846</v>
+        <v>0.3204473999129566</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005190114861307296</v>
+        <v>8.511662500337389e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.956057981787651</v>
+        <v>0.3204677840652196</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001713256390037807</v>
+        <v>2.624758159560671e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.955877852166094</v>
+        <v>0.3204317484360829</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>1.07205380308973e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.955873835160503</v>
+        <v>0.320426922387298</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>2.338588390325519e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.955876799673248</v>
+        <v>0.3204233177099672</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.955870247787519</v>
+        <v>0.3204180073328214</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.955870626355763</v>
+        <v>0.3204140830464703</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.955863959391893</v>
+        <v>0.3204137509431471</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.955860097316797</v>
+        <v>0.3204141314782049</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.955855550004612</v>
+        <v>0.3204143597992395</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.955855639949262</v>
+        <v>0.3204144497438895</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.955854782015677</v>
+        <v>0.3204135918103047</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.955855010336712</v>
+        <v>0.3204138201313393</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.9558542146725</v>
+        <v>0.3204130244671276</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.955854276941873</v>
+        <v>0.3204130867365007</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.95585430461715</v>
+        <v>0.3204131144117776</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.955854456831173</v>
+        <v>0.3204132666258009</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.955854110890211</v>
+        <v>0.3204129206848391</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.955854186997223</v>
+        <v>0.3204129967918508</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.955854353048884</v>
+        <v>0.3204131628435123</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.955854712827484</v>
+        <v>0.3204135226221124</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.955854733583942</v>
+        <v>0.3204135433785701</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.95585483736623</v>
+        <v>0.3204136471608586</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.955855065687265</v>
+        <v>0.3204138754818933</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.955854941148519</v>
+        <v>0.3204137509431471</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.955854968823796</v>
+        <v>0.320413778618424</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.95585502417435</v>
+        <v>0.3204138339689779</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.955855287089481</v>
+        <v>0.3204140968841086</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.95585520406365</v>
+        <v>0.3204140138582778</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.955854996499073</v>
+        <v>0.320413806293701</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.955855010336712</v>
+        <v>0.3204138201313393</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.955855148713096</v>
+        <v>0.3204139585077241</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.955854865041508</v>
+        <v>0.3204136748361355</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.955854692071027</v>
+        <v>0.3204135018656547</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.955854588288738</v>
+        <v>0.3204133980833662</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.955854733583942</v>
+        <v>0.3204135433785701</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.955854975742615</v>
+        <v>0.3204137855372434</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.955854802772135</v>
+        <v>0.3204136125667624</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.955854505262907</v>
+        <v>0.3204133150575354</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.955854491425269</v>
+        <v>0.3204133012198969</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.955854124727849</v>
+        <v>0.3204129345224777</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.955854124727849</v>
+        <v>0.3204129345224777</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.955854062458477</v>
+        <v>0.3204128722531046</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.955853958676188</v>
+        <v>0.3204127684708161</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.955853785705707</v>
+        <v>0.3204125955003354</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.955853834137442</v>
+        <v>0.3204126439320699</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.955853474358842</v>
+        <v>0.3204122841534698</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.955853432845926</v>
+        <v>0.3204122426405545</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.95585348819648</v>
+        <v>0.3204122979911082</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.955853543547034</v>
+        <v>0.3204123533416621</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.95585358505995</v>
+        <v>0.3204123948545775</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.955853315225999</v>
+        <v>0.3204121250206274</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.955853370576553</v>
+        <v>0.3204121803711814</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.955853515871757</v>
+        <v>0.3204123256663852</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.955853481277661</v>
+        <v>0.320412291072289</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.955853467440023</v>
+        <v>0.3204122772346504</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.955853557384672</v>
+        <v>0.3204123671793007</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.955853875650357</v>
+        <v>0.3204126854449853</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.955853695761057</v>
+        <v>0.3204125055556851</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.955853737273972</v>
+        <v>0.3204125470686006</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.955853550465853</v>
+        <v>0.3204123602604813</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.955853619654045</v>
+        <v>0.3204124294486737</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.955853419008288</v>
+        <v>0.3204122288029159</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.955853460521203</v>
+        <v>0.3204122703158313</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7867500136927612</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.95585348819648</v>
+        <v>0.3204122979911082</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386750013692761</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.503542575915646</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386750013692761</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002591839305629255</v>
+        <v>-5.223888025269843e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3335896976288547</v>
+        <v>0.0672355080980595</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.503542575915646</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6678111293160394</v>
+        <v>0.134598258119598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07703967000539425</v>
+        <v>-0.01552744241641406</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.503542575915646</v>
+        <v>-1.076714909199301</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2562908436928973</v>
+        <v>0.05165582680139272</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2562908436928973</v>
+        <v>0.05165582680139272</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.386750013692761</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2560183975694678</v>
+        <v>0.05152898664054554</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8370134129136547</v>
+        <v>0.3896802434891801</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.931711912735299</v>
+        <v>0.8316657432473525</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1601530853837934</v>
+        <v>0.07456092380963797</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.41378321331946</v>
+        <v>0.5905384846780691</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2805231001256899</v>
+        <v>0.1306007468048081</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.814755269477365</v>
+        <v>0.7772154795369068</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1536246580315473</v>
+        <v>0.07152148332730003</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.84123973296507</v>
+        <v>0.7895456063953282</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06344922104707135</v>
+        <v>0.02953941420208985</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.814352387472299</v>
+        <v>0.7770278916371546</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07905277499944022</v>
+        <v>0.03680406561415431</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.909018972535161</v>
+        <v>0.8211011731651737</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04759939139119661</v>
+        <v>0.0221602109754886</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.925112517321712</v>
+        <v>0.8285937364449434</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0361883335185099</v>
+        <v>0.01684861565026262</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.949870068940208</v>
+        <v>0.8401201057510465</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01600698848396014</v>
+        <v>0.007448779787486314</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.945661997331182</v>
+        <v>0.8381583919356326</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01269938090335914</v>
+        <v>0.005909586702080046</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.955051553490028</v>
+        <v>0.8425275727237563</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006296228783265414</v>
+        <v>0.00292923634885682</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.954934092195183</v>
+        <v>0.8424702038873718</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003657683738747592</v>
+        <v>0.001699791636938911</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.955952813739853</v>
+        <v>0.842941912029335</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001827796469746611</v>
+        <v>0.0008473958184694554</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.955945531784525</v>
+        <v>0.8429358507389999</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009005141711502362</v>
+        <v>0.0004175732798701102</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.103542575915646</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.955917609602846</v>
+        <v>0.8429201537208829</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005190114861307296</v>
+        <v>0.0002386486527868998</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.103542575915646</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.956057981787651</v>
+        <v>0.8429829951769684</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001713256390037807</v>
+        <v>7.75828942169606e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.955877852166094</v>
+        <v>0.8428959724428213</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>3.542424065087878e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.955873835160503</v>
+        <v>0.8428914335835844</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.955876799673248</v>
+        <v>0.8428902182600773</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>6.850902234816308e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.955870247787519</v>
+        <v>0.8428844423172127</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.955870626355763</v>
+        <v>0.8428821334124107</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.955863959391893</v>
+        <v>0.8428761338788141</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.955860097316797</v>
+        <v>0.8428718912686601</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.386750013692761</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.955855550004612</v>
+        <v>0.8428721195896948</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.103542575915646</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.955855639949262</v>
+        <v>0.8428722095343447</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.955854782015677</v>
+        <v>0.8428713516007599</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.955855010336712</v>
+        <v>0.8428715799217946</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692761</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.9558542146725</v>
+        <v>0.8428707842575829</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.955854276941873</v>
+        <v>0.842870846526956</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.95585430461715</v>
+        <v>0.8428708742022328</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.955854456831173</v>
+        <v>0.8428710264162561</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.955854110890211</v>
+        <v>0.8428706804752943</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.955854186997223</v>
+        <v>0.842870756582306</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.386750013692761</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.955854353048884</v>
+        <v>0.8428709226339676</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.9052000093893221</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.955854712827484</v>
+        <v>0.8428712824125676</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.955854733583942</v>
+        <v>0.8428713031690254</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.95585483736623</v>
+        <v>0.8428714069513138</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.955855065687265</v>
+        <v>0.8428716352723485</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.955854941148519</v>
+        <v>0.8428715107336023</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.955854968823796</v>
+        <v>0.8428715384088792</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.95585502417435</v>
+        <v>0.8428715937594331</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.955855287089481</v>
+        <v>0.8428718566745639</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.95585520406365</v>
+        <v>0.842871773648733</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.955854996499073</v>
+        <v>0.8428715660841563</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.955855010336712</v>
+        <v>0.8428715799217946</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.955855148713096</v>
+        <v>0.8428717182981793</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.955854865041508</v>
+        <v>0.8428714346265906</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.955854692071027</v>
+        <v>0.8428712616561099</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.955854588288738</v>
+        <v>0.8428711578738215</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.955854733583942</v>
+        <v>0.8428713031690254</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.955854975742615</v>
+        <v>0.8428715453276986</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.955854802772135</v>
+        <v>0.8428713723572175</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.955854505262907</v>
+        <v>0.8428710748479906</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.955854491425269</v>
+        <v>0.8428710610103521</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.955854124727849</v>
+        <v>0.8428706943129329</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.955854124727849</v>
+        <v>0.8428706943129329</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.955854062458477</v>
+        <v>0.8428706320435598</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.955853958676188</v>
+        <v>0.8428705282612713</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.955853785705707</v>
+        <v>0.8428703552907906</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.955853834137442</v>
+        <v>0.8428704037225251</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.955853474358842</v>
+        <v>0.8428700439439251</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.955853432845926</v>
+        <v>0.8428700024310096</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.95585348819648</v>
+        <v>0.8428700577815633</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.955853543547034</v>
+        <v>0.8428701131321173</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.95585358505995</v>
+        <v>0.8428701546450327</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.955853315225999</v>
+        <v>0.8428698848110826</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.955853370576553</v>
+        <v>0.8428699401616365</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.955853515871757</v>
+        <v>0.8428700854568405</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.955853481277661</v>
+        <v>0.8428700508627442</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.955853467440023</v>
+        <v>0.8428700370251057</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.955853557384672</v>
+        <v>0.8428701269697558</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.955853875650357</v>
+        <v>0.8428704452354405</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.955853695761057</v>
+        <v>0.8428702653461404</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.955853737273972</v>
+        <v>0.8428703068590557</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.955853550465853</v>
+        <v>0.8428701200509364</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.955853619654045</v>
+        <v>0.8428701892391289</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.955853419008288</v>
+        <v>0.8428699885933711</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.955853460521203</v>
+        <v>0.8428700301062865</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7867500136927612</v>
+        <v>0.705200009389322</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.95585348819648</v>
+        <v>0.8428700577815633</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.1970933675765991</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.09615729749202728</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01486009731888771</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.02192795276641846</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4160766030030929</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.03984915465116501</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.03946545720100403</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.04015052318572998</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.03393995016813278</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.02842993289232254</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.03110386431217194</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.03272775560617447</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.03412339836359024</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.02991653978824615</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.03151153773069382</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.03413421660661697</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.03601093590259552</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.03353486210107803</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.03065725415945053</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.02501276135444641</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.02714207023382187</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.03235597163438797</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.03486950695514679</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.03596162796020508</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.02872658520936966</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.03093699365854263</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.02286695688962936</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.00955432653427124</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01547697558999062</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.02282482013106346</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.02236701548099518</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.02500329911708832</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.02769607305526733</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.02624364197254181</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.01551175117492676</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.01839252933859825</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.02166107296943665</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.01876889541745186</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.02164577692747116</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.02245128527283669</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.01796532049775124</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.008995629847049713</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0009013265371322632</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.007211219519376755</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-5.223888025269843e-05</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.0672355080980595</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.005985062569379807</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.134598258119598</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.01552744241641406</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01645676791667938</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.076714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.05165582680139272</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.002792965620756149</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.05165582680139272</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.00811200775206089</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2445617031931146</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.05152898664054554</v>
+        <v>0.2122441086671844</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.3896802434891801</v>
+        <v>0.4540855127196219</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.003120690584182739</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8316657432473525</v>
+        <v>1.121319324494719</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.07456092380963797</v>
+        <v>0.08688414638061634</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0135936327278614</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5905384846780691</v>
+        <v>0.8403394555965972</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1306007468048081</v>
+        <v>0.1521856047754329</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01211976259946823</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7772154795369068</v>
+        <v>1.057869544186717</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.07152148332730003</v>
+        <v>0.08334261356182819</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01032483763992786</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7895456063953282</v>
+        <v>1.072237556290608</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.02953941420208985</v>
+        <v>0.03442151633212544</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01111561805009842</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7770278916371546</v>
+        <v>1.057651000352126</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.03680406561415431</v>
+        <v>0.0428862554943177</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01813226006925106</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8211011731651737</v>
+        <v>1.109008360605669</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0221602109754886</v>
+        <v>0.02582306552668471</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01211412250995636</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8285937364449434</v>
+        <v>1.117739334232866</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01684861565026262</v>
+        <v>0.01963247176985616</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.009729253128170967</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8401201057510465</v>
+        <v>1.131170793509005</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.007448779787486314</v>
+        <v>0.008682070430362513</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.005204860121011734</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8381583919356326</v>
+        <v>1.128885566820929</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.005909586702080046</v>
+        <v>0.006888204885622501</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.0103609710931778</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8425275727237563</v>
+        <v>1.133977404075083</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00292923634885682</v>
+        <v>0.003412022039674694</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.02539827674627304</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8424702038873718</v>
+        <v>1.133911397955879</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001699791636938911</v>
+        <v>0.001981984109264976</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01421733200550079</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.842941912029335</v>
+        <v>1.134461947554102</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0008473958184694554</v>
+        <v>0.000989946655005303</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.04297120124101639</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8429358507389999</v>
+        <v>1.134455708778352</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0004175732798701102</v>
+        <v>0.0004865648357672711</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.03219347447156906</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8429201537208829</v>
+        <v>1.134438265308299</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002386486527868998</v>
+        <v>0.0002787004861217326</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.02995941787958145</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8429829951769684</v>
+        <v>1.134512182582773</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>7.75828942169606e-05</v>
+        <v>9.097471490079203e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.002332080155611038</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8428959724428213</v>
+        <v>1.13441185886471</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.542424065087878e-05</v>
+        <v>4.21616140926919e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02723777666687965</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8428914335835844</v>
+        <v>1.134407394555993</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.701576517097656e-05</v>
+        <v>2.190815743119357e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.03643721714615822</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8428902182600773</v>
+        <v>1.134406775038003</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.04347735643386841</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8428844423172127</v>
+        <v>1.134400922988126</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>8.184014912590811e-07</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.02448864467442036</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8428821334124107</v>
+        <v>1.134399150129074</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.02065001428127289</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8428761338788141</v>
+        <v>1.134393150595477</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01158119738101959</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8428718912686601</v>
+        <v>1.134388907985323</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.002803690731525421</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8428721195896948</v>
+        <v>1.134389136306358</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.001899518072605133</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8428722095343447</v>
+        <v>1.134389226251008</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01929451525211334</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8428713516007599</v>
+        <v>1.134388368317423</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.02131922170519829</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8428715799217946</v>
+        <v>1.134388596638458</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.03316761925816536</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8428707842575829</v>
+        <v>1.134387800974246</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.03251612931489944</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.842870846526956</v>
+        <v>1.134387863243619</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.03322810679674149</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8428708742022328</v>
+        <v>1.134387890918896</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.03099908120930195</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8428710264162561</v>
+        <v>1.134388043132919</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.02921294420957565</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8428706804752943</v>
+        <v>1.134387697191957</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.03109563514590263</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.842870756582306</v>
+        <v>1.134387773298969</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.02604450099170208</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8428709226339676</v>
+        <v>1.134387939350631</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02610530704259872</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8428712824125676</v>
+        <v>1.13438829912923</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0218217745423317</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8428713031690254</v>
+        <v>1.134388319885688</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01661776378750801</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8428714069513138</v>
+        <v>1.134388423667977</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.00853332132101059</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8428716352723485</v>
+        <v>1.134388651989012</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01454441249370575</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8428715107336023</v>
+        <v>1.134388527450265</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0247153528034687</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8428715384088792</v>
+        <v>1.134388555125542</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.03336461260914803</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.705200009389322</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8428715937594331</v>
+        <v>1.134388610476096</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.02430944889783859</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8428718566745639</v>
+        <v>1.134388873391227</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.02276420965790749</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.705200009389322</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.842871773648733</v>
+        <v>1.134388790365396</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.02896253205835819</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8428715660841563</v>
+        <v>1.134388582800819</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.03242813795804977</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8428715799217946</v>
+        <v>1.134388596638458</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.0305212177336216</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8428717182981793</v>
+        <v>1.134388735014842</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03133340179920197</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8428714346265906</v>
+        <v>1.134388451343254</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.03431164473295212</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8428712616561099</v>
+        <v>1.134388278372773</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.04068148881196976</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.705200009389322</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8428711578738215</v>
+        <v>1.134388174590485</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.03711488097906113</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.705200009389322</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8428713031690254</v>
+        <v>1.134388319885688</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02835758402943611</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8428715453276986</v>
+        <v>1.134388562044362</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.02377737499773502</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8428713723572175</v>
+        <v>1.134388389073881</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.02867050841450691</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8428710748479906</v>
+        <v>1.134388091564654</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02639378979802132</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.16</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8428710610103521</v>
+        <v>1.134388077727015</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.02903264760971069</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8428706943129329</v>
+        <v>1.134387711029596</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.03123840503394604</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8428706943129329</v>
+        <v>1.134387711029596</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.02661233581602573</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8428706320435598</v>
+        <v>1.134387648760223</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0187222808599472</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8428705282612713</v>
+        <v>1.134387544977934</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01833529956638813</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8428703552907906</v>
+        <v>1.134387372007453</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01607713289558887</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8428704037225251</v>
+        <v>1.134387420439188</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.01503638178110123</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8428700439439251</v>
+        <v>1.134387060660588</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0145491398870945</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8428700024310096</v>
+        <v>1.134387019147673</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01493753679096699</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8428700577815633</v>
+        <v>1.134387074498227</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.00977221317589283</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8428701131321173</v>
+        <v>1.134387129848781</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.006126865744590759</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8428701546450327</v>
+        <v>1.134387171361696</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.006026305258274078</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8428698848110826</v>
+        <v>1.134386901527746</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.008487626910209656</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8428699401616365</v>
+        <v>1.134386956878299</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.00607212632894516</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8428700854568405</v>
+        <v>1.134387102173503</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.007228784263134003</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8428700508627442</v>
+        <v>1.134387067579407</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.005671501159667969</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8428700370251057</v>
+        <v>1.134387053741769</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01443108543753624</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8428701269697558</v>
+        <v>1.134387143686419</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.02136353030800819</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8428704452354405</v>
+        <v>1.134387461952103</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.007613569498062134</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8428702653461404</v>
+        <v>1.134387282062803</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.002159543335437775</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8428703068590557</v>
+        <v>1.134387323575719</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.00820455327630043</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8428701200509364</v>
+        <v>1.1343871367676</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.008638408035039902</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8428701892391289</v>
+        <v>1.134387205955792</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.01335490308701992</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8428699885933711</v>
+        <v>1.134387005310034</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01321632415056229</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.705200009389322</v>
+        <v>-0.1199999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8428700301062865</v>
+        <v>1.13438704682295</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01527648977935314</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.705200009389322</v>
+        <v>0.02000000000000046</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8428700577815633</v>
+        <v>1.134387074498227</v>
       </c>
     </row>
   </sheetData>
